--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123182530</v>
+        <v>123201149</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628725</v>
+        <v>628811</v>
       </c>
       <c r="R2" t="n">
-        <v>6896027</v>
+        <v>6896051</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Snötäckt mark, oklart hur många plantor</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123201149</v>
+        <v>123201103</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -826,16 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628811</v>
+        <v>628774</v>
       </c>
       <c r="R3" t="n">
-        <v>6896051</v>
+        <v>6896003</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123201103</v>
+        <v>123182530</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -938,21 +938,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628774</v>
+        <v>628725</v>
       </c>
       <c r="R4" t="n">
-        <v>6896003</v>
+        <v>6896027</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Snötäckt mark, oklart hur många plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123201149</v>
+        <v>123182530</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628811</v>
+        <v>628725</v>
       </c>
       <c r="R2" t="n">
-        <v>6896051</v>
+        <v>6896027</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Snötäckt mark, oklart hur många plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123182530</v>
+        <v>123201149</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628725</v>
+        <v>628811</v>
       </c>
       <c r="R4" t="n">
-        <v>6896027</v>
+        <v>6896051</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Snötäckt mark, oklart hur många plantor</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123182530</v>
+        <v>123201103</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628725</v>
+        <v>628774</v>
       </c>
       <c r="R2" t="n">
-        <v>6896027</v>
+        <v>6896003</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Snötäckt mark, oklart hur många plantor</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123201103</v>
+        <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628774</v>
+        <v>628725</v>
       </c>
       <c r="R3" t="n">
-        <v>6896003</v>
+        <v>6896027</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Snötäckt mark, oklart hur många plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
         <v>123201149</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123201103</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>123201149</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123201103</v>
+        <v>123201149</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628774</v>
+        <v>628811</v>
       </c>
       <c r="R2" t="n">
-        <v>6896003</v>
+        <v>6896051</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +790,7 @@
         <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123201149</v>
+        <v>123201103</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,16 +938,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628811</v>
+        <v>628774</v>
       </c>
       <c r="R4" t="n">
-        <v>6896051</v>
+        <v>6896003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123201149</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>123201103</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123201149</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123182530</v>
+        <v>123201103</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628725</v>
+        <v>628774</v>
       </c>
       <c r="R3" t="n">
-        <v>6896027</v>
+        <v>6896003</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Snötäckt mark, oklart hur många plantor</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123201103</v>
+        <v>123182530</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,21 +938,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628774</v>
+        <v>628725</v>
       </c>
       <c r="R4" t="n">
-        <v>6896003</v>
+        <v>6896027</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Snötäckt mark, oklart hur många plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123201149</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123201103</v>
+        <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628774</v>
+        <v>628725</v>
       </c>
       <c r="R3" t="n">
-        <v>6896003</v>
+        <v>6896027</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Snötäckt mark, oklart hur många plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123182530</v>
+        <v>123201103</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,16 +938,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628725</v>
+        <v>628774</v>
       </c>
       <c r="R4" t="n">
-        <v>6896027</v>
+        <v>6896003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Snötäckt mark, oklart hur många plantor</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123201149</v>
+        <v>123201103</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628811</v>
+        <v>628774</v>
       </c>
       <c r="R2" t="n">
-        <v>6896051</v>
+        <v>6896003</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +795,7 @@
         <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123201103</v>
+        <v>123201149</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,21 +943,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storängesbäcken, Storängesbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628774</v>
+        <v>628811</v>
       </c>
       <c r="R4" t="n">
-        <v>6896003</v>
+        <v>6896051</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>123211028</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4900-2025 artfynd.xlsx
+++ b/artfynd/A 4900-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123201103</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>123182530</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>123201149</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
